--- a/data/trans_camb/IP2002-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 10,37</t>
+          <t>-2,6; 10,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 5,9</t>
+          <t>-7,14; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 0,55</t>
+          <t>-10,02; 1,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 9,44</t>
+          <t>-6,75; 9,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 0,14</t>
+          <t>-12,95; -0,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,49; -1,31</t>
+          <t>-13,8; -1,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 8,21</t>
+          <t>-2,63; 7,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,81</t>
+          <t>-8,56; 0,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -2,09</t>
+          <t>-10,28; -1,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,37; 249,0</t>
+          <t>-30,4; 265,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-79,65; 143,83</t>
+          <t>-78,08; 153,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 86,56</t>
+          <t>-100,0; 77,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,89; 182,74</t>
+          <t>-54,62; 171,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-92,4; 27,02</t>
+          <t>-100,0; 33,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 8,15</t>
+          <t>-100,0; 23,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 142,67</t>
+          <t>-25,11; 134,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,91; 16,03</t>
+          <t>-80,06; 19,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,84; -9,65</t>
+          <t>-92,65; -13,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,19</t>
+          <t>-5,32; 0,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,56</t>
+          <t>-3,49; 2,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 0,79</t>
+          <t>-5,09; 0,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,23</t>
+          <t>-3,18; 2,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,24</t>
+          <t>-4,87; 0,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; -0,4</t>
+          <t>-5,9; -0,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,62</t>
+          <t>-3,34; 0,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,41</t>
+          <t>-3,34; 0,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -0,69</t>
+          <t>-4,78; -0,89</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 4,58</t>
+          <t>-58,8; 9,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,06; 44,15</t>
+          <t>-38,01; 38,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,59; 16,21</t>
+          <t>-57,99; 14,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 37,14</t>
+          <t>-38,06; 35,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 5,39</t>
+          <t>-55,22; 4,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,49; -5,35</t>
+          <t>-65,56; -8,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 9,79</t>
+          <t>-39,78; 11,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 6,38</t>
+          <t>-38,46; 10,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,52; -10,49</t>
+          <t>-55,63; -13,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 1,19</t>
+          <t>-6,51; 1,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 2,54</t>
+          <t>-5,73; 2,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 8,32</t>
+          <t>-1,75; 7,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 3,56</t>
+          <t>-4,94; 3,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 2,9</t>
+          <t>-5,55; 3,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 7,9</t>
+          <t>-2,43; 7,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 1,21</t>
+          <t>-4,36; 1,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,56</t>
+          <t>-4,26; 1,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 6,59</t>
+          <t>-0,4; 6,47</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,51; 41,66</t>
+          <t>-76,32; 43,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,08; 79,94</t>
+          <t>-70,62; 62,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 205,64</t>
+          <t>-24,72; 197,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,43; 106,51</t>
+          <t>-63,83; 102,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,95; 80,89</t>
+          <t>-67,74; 80,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 233,14</t>
+          <t>-35,29; 220,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-61,05; 30,66</t>
+          <t>-58,42; 35,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,0; 34,86</t>
+          <t>-57,31; 33,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 156,6</t>
+          <t>-7,89; 145,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,76</t>
+          <t>-3,96; 0,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,29</t>
+          <t>-3,2; 1,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,16</t>
+          <t>-3,52; 1,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,94</t>
+          <t>-2,7; 1,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,42</t>
+          <t>-4,55; -0,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,0</t>
+          <t>-4,43; -0,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,54</t>
+          <t>-2,58; 0,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -0,23</t>
+          <t>-3,23; -0,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; -0,31</t>
+          <t>-3,33; -0,15</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 13,39</t>
+          <t>-47,71; 7,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 21,72</t>
+          <t>-36,57; 27,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 19,61</t>
+          <t>-41,26; 17,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 32,87</t>
+          <t>-31,8; 30,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-54,42; -6,51</t>
+          <t>-53,17; -3,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,13; 0,31</t>
+          <t>-52,8; -1,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 8,83</t>
+          <t>-32,16; 10,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,86; -3,07</t>
+          <t>-40,81; -1,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,82; -4,01</t>
+          <t>-40,45; -1,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2002-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 10,9</t>
+          <t>-2,73; 10,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 6,34</t>
+          <t>-7,02; 6,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 1,23</t>
+          <t>-10,2; 1,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 9,94</t>
+          <t>-6,37; 9,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -0,33</t>
+          <t>-12,35; -0,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,8; -1,57</t>
+          <t>-12,81; -1,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,7</t>
+          <t>-2,74; 7,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 0,83</t>
+          <t>-8,06; 1,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,28; -1,86</t>
+          <t>-9,86; -1,51</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 265,76</t>
+          <t>-29,02; 228,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,08; 153,66</t>
+          <t>-76,37; 174,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,97</t>
+          <t>-100,0; 83,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 171,39</t>
+          <t>-53,31; 184,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 33,43</t>
+          <t>-92,69; 20,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 23,01</t>
+          <t>-100,0; 20,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 134,69</t>
+          <t>-29,88; 133,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,06; 19,9</t>
+          <t>-77,96; 28,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-92,65; -13,25</t>
+          <t>-92,6; -11,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,55</t>
+          <t>-5,13; 0,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,22</t>
+          <t>-3,39; 2,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,84</t>
+          <t>-5,1; 0,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,18</t>
+          <t>-3,36; 2,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,21</t>
+          <t>-5,27; 0,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,81</t>
+          <t>-5,8; -0,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,67</t>
+          <t>-3,34; 0,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,61</t>
+          <t>-3,18; 0,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; -0,89</t>
+          <t>-4,6; -0,89</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,8; 9,22</t>
+          <t>-58,16; 9,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 38,05</t>
+          <t>-37,09; 39,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 14,27</t>
+          <t>-57,68; 16,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 35,74</t>
+          <t>-38,66; 40,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,22; 4,78</t>
+          <t>-55,68; 7,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,56; -8,74</t>
+          <t>-63,53; -5,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 11,36</t>
+          <t>-39,62; 10,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 10,89</t>
+          <t>-38,28; 9,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,63; -13,32</t>
+          <t>-54,25; -12,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 1,46</t>
+          <t>-5,91; 1,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 2,29</t>
+          <t>-5,67; 2,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 7,73</t>
+          <t>-2,32; 7,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,17</t>
+          <t>-5,0; 3,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 3,03</t>
+          <t>-5,21; 3,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 7,34</t>
+          <t>-2,63; 7,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,32</t>
+          <t>-4,36; 1,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,32</t>
+          <t>-4,41; 1,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 6,47</t>
+          <t>-0,57; 6,33</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,32; 43,7</t>
+          <t>-75,92; 64,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 62,3</t>
+          <t>-71,34; 77,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 197,25</t>
+          <t>-32,44; 193,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,83; 102,97</t>
+          <t>-63,06; 95,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 80,88</t>
+          <t>-66,48; 98,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 220,38</t>
+          <t>-37,42; 206,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 35,34</t>
+          <t>-57,27; 34,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,31; 33,11</t>
+          <t>-57,74; 45,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 145,52</t>
+          <t>-11,34; 143,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,49</t>
+          <t>-3,85; 0,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,5</t>
+          <t>-3,12; 1,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,05</t>
+          <t>-3,43; 1,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,86</t>
+          <t>-2,59; 1,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -0,22</t>
+          <t>-4,64; -0,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; -0,12</t>
+          <t>-4,2; 0,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 0,68</t>
+          <t>-2,59; 0,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,1</t>
+          <t>-3,28; -0,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; -0,15</t>
+          <t>-3,38; -0,2</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 7,83</t>
+          <t>-46,26; 9,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 27,92</t>
+          <t>-38,22; 23,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,26; 17,5</t>
+          <t>-41,36; 17,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 30,02</t>
+          <t>-30,47; 31,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,17; -3,18</t>
+          <t>-54,29; -5,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,8; -1,86</t>
+          <t>-51,38; 2,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 10,48</t>
+          <t>-32,68; 10,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,81; -1,67</t>
+          <t>-40,59; -1,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,45; -1,73</t>
+          <t>-42,13; -2,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2002-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-6,14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,99</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,76</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,22</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,76</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-6,14</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,03</t>
+          <t>-4,43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,88</t>
+          <t>-5,71</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 10,86</t>
+          <t>-6,33; 9,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 6,79</t>
+          <t>-11,93; 0,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 1,01</t>
+          <t>-13,52; -0,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 9,5</t>
+          <t>-3,39; 10,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,35; -0,25</t>
+          <t>-7,31; 5,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -1,16</t>
+          <t>-10,26; 1,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 7,66</t>
+          <t>-2,06; 8,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,17</t>
+          <t>-7,95; 0,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -1,51</t>
+          <t>-10,02; -1,71</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,24%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-67,69%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-77,02%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>51,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-16,79%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-65,68%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-67,69%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-77,51%</t>
+          <t>-61,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-72,3%</t>
+          <t>-70,28%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 228,4</t>
+          <t>-51,89; 182,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,37; 174,18</t>
+          <t>-92,4; 27,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 83,82</t>
+          <t>-100,0; 23,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,31; 184,85</t>
+          <t>-33,37; 249,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-92,69; 20,73</t>
+          <t>-79,65; 143,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 20,76</t>
+          <t>-100,0; 88,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 133,11</t>
+          <t>-21,01; 142,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,96; 28,89</t>
+          <t>-78,91; 16,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-92,6; -11,06</t>
+          <t>-91,81; -7,56</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,58</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,19</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,22</t>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,74</t>
+          <t>-2,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 0,53</t>
+          <t>-3,5; 2,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,34</t>
+          <t>-4,92; 0,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,82</t>
+          <t>-6,02; -0,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,57</t>
+          <t>-5,34; 0,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 0,35</t>
+          <t>-3,5; 2,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -0,59</t>
+          <t>-4,79; 0,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,66</t>
+          <t>-3,39; 0,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,55</t>
+          <t>-3,38; 0,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; -0,89</t>
+          <t>-4,58; -0,65</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-6,66%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-30,84%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-42,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-32,88%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-7,67%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-29,12%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-6,66%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-30,84%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-43,21%</t>
+          <t>-27,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-36,51%</t>
+          <t>-35,38%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 9,02</t>
+          <t>-38,36; 37,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 39,23</t>
+          <t>-55,33; 5,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 16,05</t>
+          <t>-65,81; -3,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,66; 40,86</t>
+          <t>-57,26; 4,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 7,44</t>
+          <t>-39,06; 44,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,53; -5,15</t>
+          <t>-52,97; 16,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,62; 10,92</t>
+          <t>-39,63; 9,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,28; 9,75</t>
+          <t>-39,51; 6,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,25; -12,47</t>
+          <t>-54,15; -9,72</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,77</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,18</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,71</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 1,69</t>
+          <t>-4,82; 3,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 2,68</t>
+          <t>-5,59; 2,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,83</t>
+          <t>-2,48; 7,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,34</t>
+          <t>-6,76; 1,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 3,48</t>
+          <t>-5,99; 2,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,45</t>
+          <t>-1,16; 8,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,36</t>
+          <t>-4,44; 1,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 1,6</t>
+          <t>-4,4; 1,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 6,33</t>
+          <t>-0,75; 6,63</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-13,4%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-19,98%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37,84%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-38,4%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-28,6%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>50,57%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-13,4%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-19,98%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,92; 64,99</t>
+          <t>-62,43; 106,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,34; 77,53</t>
+          <t>-69,95; 80,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 193,53</t>
+          <t>-36,49; 220,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,06; 95,0</t>
+          <t>-76,51; 41,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 98,71</t>
+          <t>-72,08; 79,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 206,2</t>
+          <t>-16,25; 212,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,27; 34,42</t>
+          <t>-61,05; 30,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,74; 45,45</t>
+          <t>-59,0; 34,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 143,45</t>
+          <t>-11,61; 155,73</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,48</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,31</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,89</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,17</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,48</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-1,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,52</t>
+          <t>-2,56; 1,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,38</t>
+          <t>-4,54; -0,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,08</t>
+          <t>-4,42; -0,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,88</t>
+          <t>-3,76; 0,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; -0,49</t>
+          <t>-3,15; 1,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,15</t>
+          <t>-3,18; 1,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,73</t>
+          <t>-2,54; 0,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,28; -0,12</t>
+          <t>-3,25; -0,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,2</t>
+          <t>-3,38; -0,18</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,87%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-34,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-31,73%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-22,12%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-12,54%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-16,46%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-4,87%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-34,0%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-31,14%</t>
+          <t>-13,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-24,34%</t>
+          <t>-23,02%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 9,04</t>
+          <t>-30,82; 32,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 23,18</t>
+          <t>-54,42; -6,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 17,89</t>
+          <t>-53,44; -0,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 31,22</t>
+          <t>-45,78; 13,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-54,29; -5,17</t>
+          <t>-39,31; 21,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,38; 2,94</t>
+          <t>-38,31; 22,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 10,54</t>
+          <t>-32,17; 8,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,59; -1,84</t>
+          <t>-40,86; -3,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,13; -2,63</t>
+          <t>-41,46; -2,25</t>
         </is>
       </c>
     </row>
